--- a/data/data50.xlsx
+++ b/data/data50.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\科研\中医药\血脂\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\program\graph sparsification for dyslipidemia identification\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE044E24-E736-41B8-AA49-BBEDC1588574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C0A176-8FB0-4750-9B1D-85C9AF53595C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{B9FADC4B-0CDE-43BB-85EC-AF767777B3D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$LU$1:$LU$51</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3830,8 +3833,7 @@
         <v>1</v>
       </c>
       <c r="LU2" s="4">
-        <f>SUM(LE2+LG2+LI2+LK2+LL2+LM2+LN2+LO2+LP2+LQ2+LR2+LS2+LT2)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="LV2" s="4">
         <v>0</v>
@@ -7851,7 +7853,6 @@
         <v>0</v>
       </c>
       <c r="LU6" s="4">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="LV6" s="4">
@@ -8859,7 +8860,6 @@
         <v>0</v>
       </c>
       <c r="LU7" s="4">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="LV7" s="4">
@@ -10875,7 +10875,6 @@
         <v>0</v>
       </c>
       <c r="LU9" s="4">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="LV9" s="4">
@@ -11883,8 +11882,7 @@
         <v>0</v>
       </c>
       <c r="LU10" s="4">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="LV10" s="4">
         <v>1</v>
@@ -13896,7 +13894,6 @@
         <v>0</v>
       </c>
       <c r="LU12" s="4">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="LV12" s="4">
@@ -14904,7 +14901,6 @@
         <v>0</v>
       </c>
       <c r="LU13" s="4">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="LV13" s="4">
@@ -18933,7 +18929,6 @@
         <v>0</v>
       </c>
       <c r="LU17" s="4">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="LV17" s="4">
@@ -21951,8 +21946,7 @@
         <v>0</v>
       </c>
       <c r="LU20" s="4">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="LV20" s="4">
         <v>0</v>
@@ -22956,8 +22950,7 @@
         <v>1</v>
       </c>
       <c r="LU21" s="4">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="LV21" s="4">
         <v>1</v>
@@ -23964,7 +23957,6 @@
         <v>0</v>
       </c>
       <c r="LU22" s="4">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="LV22" s="4">
@@ -24972,7 +24964,6 @@
         <v>1</v>
       </c>
       <c r="LU23" s="4">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="LV23" s="4">
@@ -26985,8 +26976,7 @@
         <v>0</v>
       </c>
       <c r="LU25" s="4">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="LV25" s="4">
         <v>0</v>
@@ -27990,7 +27980,6 @@
         <v>0</v>
       </c>
       <c r="LU26" s="4">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="LV26" s="4">
@@ -29997,8 +29986,7 @@
         <v>0</v>
       </c>
       <c r="LU28" s="4">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="LV28" s="4">
         <v>0</v>
@@ -31002,8 +30990,7 @@
         <v>0</v>
       </c>
       <c r="LU29" s="4">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="LV29" s="4">
         <v>2</v>
@@ -32010,8 +31997,7 @@
         <v>1</v>
       </c>
       <c r="LU30" s="4">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="LV30" s="4">
         <v>2</v>
@@ -33018,7 +33004,6 @@
         <v>0</v>
       </c>
       <c r="LU31" s="4">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="LV31" s="4">
@@ -34026,8 +34011,7 @@
         <v>1</v>
       </c>
       <c r="LU32" s="4">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="LV32" s="4">
         <v>2</v>
@@ -35031,8 +35015,7 @@
         <v>1</v>
       </c>
       <c r="LU33" s="4">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="LV33" s="4">
         <v>0</v>
@@ -37044,7 +37027,6 @@
         <v>0</v>
       </c>
       <c r="LU35" s="4">
-        <f t="shared" ref="LU35:LU51" si="1">LE35+LG35+LI35+LK35+LL35+LM35+LN35+LO35+LP35+LQ35+LR35+LS35+LT35</f>
         <v>2</v>
       </c>
       <c r="LV35" s="4">
@@ -38052,7 +38034,7 @@
         <v>0</v>
       </c>
       <c r="LU36" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="LU35:LU51" si="1">LE36+LG36+LI36+LK36+LL36+LM36+LN36+LO36+LP36+LQ36+LR36+LS36+LT36</f>
         <v>1</v>
       </c>
       <c r="LV36" s="4">
@@ -40068,8 +40050,7 @@
         <v>0</v>
       </c>
       <c r="LU38" s="4">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="LV38" s="4">
         <v>1</v>
@@ -43092,7 +43073,6 @@
         <v>0</v>
       </c>
       <c r="LU41" s="4">
-        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="LV41" s="4">
@@ -45108,8 +45088,7 @@
         <v>1</v>
       </c>
       <c r="LU43" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="LV43" s="4">
         <v>2</v>
@@ -46113,8 +46092,7 @@
         <v>1</v>
       </c>
       <c r="LU44" s="4">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="LV44" s="4">
         <v>2</v>
@@ -49131,8 +49109,7 @@
         <v>0</v>
       </c>
       <c r="LU47" s="4">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="LV47" s="4">
         <v>0</v>
@@ -51144,7 +51121,6 @@
         <v>0</v>
       </c>
       <c r="LU49" s="4">
-        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="LV49" s="4">
@@ -53171,6 +53147,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="LU1:LU51" xr:uid="{A5674208-4F6E-43EE-8E0E-262E7DE458D8}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
